--- a/config/tables/gas.ability_task.xlsx
+++ b/config/tables/gas.ability_task.xlsx
@@ -2,98 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AbilityAction" sheetId="1" r:id="R895ebcdba7f34648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AbilityAction" sheetId="1" r:id="R52d4942727d343a2"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">##var</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ability_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">at_tick</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">order</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">kind</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">target_scope</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">effect_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##type</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">int#range=[1,1000000]</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">int#ref=gas.TbAbility</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">int#range=[0,1000000]</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">gas.ActionKind</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">gas.TargetScope</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">int?#ref=gas.TbEffect</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##group</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unique action identifier.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Owning ability identifier.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fixed ticks after activation. Zero executes on activation.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Action order among actions at the same tick.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Apply an effect or end the owning ability.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Captured targets used by ApplyEffect. None for EndAbility.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Effect identifier for ApplyEffect. Blank for EndAbility.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ApplyEffect</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Primary</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EndAbility</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">None</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1099,146 +1014,118 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" customWidth="1"/>
-    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="8" width="23" customWidth="1"/>
+    <x:col min="3" max="3" width="23" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>7</x:v>
+      <x:c r="A1" s="1" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="str">
+        <x:v>at_tick</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="str">
+        <x:v>kind</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="str">
+        <x:v>target_scope</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="str">
+        <x:v>effect_id</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="52" customHeight="1">
-      <x:c r="A2" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>14</x:v>
+      <x:c r="A2" s="2" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>int#range=[1,1000000]</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="str">
+        <x:v>int#range=[0,1000000]</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="str">
+        <x:v>gas.ActionKind</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="str">
+        <x:v>gas.TargetScope</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="str">
+        <x:v>int?#ref=gas.TbEffect</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
-      <x:c r="A3" s="3" t="s">
-        <x:v>15</x:v>
+      <x:c r="A3" s="3" t="str">
+        <x:v>##group</x:v>
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3"/>
       <x:c r="D3" s="3"/>
       <x:c r="E3" s="3"/>
       <x:c r="F3" s="3"/>
-      <x:c r="G3" s="3"/>
-      <x:c r="H3" s="3"/>
     </x:row>
     <x:row r="4" ht="66" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="s">
-        <x:v>23</x:v>
+      <x:c r="A4" s="4" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>Unique action identifier.</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="str">
+        <x:v>Fixed ticks after activation. Zero executes on activation.</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="str">
+        <x:v>Apply an effect or end the owning ability.</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="str">
+        <x:v>Captured targets used by ApplyEffect. None for EndAbility.</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str">
+        <x:v>Effect identifier for ApplyEffect. Blank for EndAbility.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
       <x:c r="A5" s="5"/>
-      <x:c r="B5" s="6">
+      <x:c r="B5" s="6" t="n">
         <x:v>10011</x:v>
       </x:c>
-      <x:c r="C5" s="6">
-        <x:v>1001</x:v>
-      </x:c>
-      <x:c r="D5" s="6">
+      <x:c r="C5" s="6" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E5" s="6">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G5" s="5" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H5" s="6">
+      <x:c r="D5" s="5" t="str">
+        <x:v>ApplyEffect</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="n">
         <x:v>2003</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="5"/>
-      <x:c r="B6" s="6">
+      <x:c r="B6" s="6" t="n">
         <x:v>10012</x:v>
       </x:c>
-      <x:c r="C6" s="6">
-        <x:v>1001</x:v>
-      </x:c>
-      <x:c r="D6" s="6">
+      <x:c r="C6" s="6" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E6" s="6">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="5" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G6" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H6" s="6"/>
+      <x:c r="D6" s="5" t="str">
+        <x:v>EndAbility</x:v>
+      </x:c>
+      <x:c r="E6" s="5" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="F6" s="6"/>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
       <x:c r="A7" s="8"/>
@@ -1246,34 +1133,28 @@
         <x:v>10021</x:v>
       </x:c>
       <x:c r="C7" s="9" t="n">
-        <x:v>1002</x:v>
-      </x:c>
-      <x:c r="D7" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E7" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="str">
+      <x:c r="D7" s="8" t="str">
         <x:v>EndAbility</x:v>
       </x:c>
-      <x:c r="G7" s="8" t="str">
+      <x:c r="E7" s="8" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="H7" s="9"/>
+      <x:c r="F7" s="9"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="4">
-    <x:dataValidation type="list" sqref="F5:F6">
+    <x:dataValidation type="list" sqref="D5:D6">
       <x:formula1>"ApplyEffect,EndAbility"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="G5:G6">
+    <x:dataValidation type="list" sqref="E5:E6">
       <x:formula1>"None,Primary,AllCaptured"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="F7">
+    <x:dataValidation type="list" sqref="D7">
       <x:formula1>"ApplyEffect,EndAbility"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="G7">
+    <x:dataValidation type="list" sqref="E7">
       <x:formula1>"None,Primary,AllCaptured"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
